--- a/jpcore-r4/develop/CodeSystem-jp-simpleobservationcategory-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-simpleobservationcategory-cs.xlsx
@@ -231,7 +231,7 @@
     <t>Procedure</t>
   </si>
   <si>
-    <t>他の手順によって生成された観察。 このカテゴリには、実験室および画像検査 (心臓カテーテル法、内視鏡検査、電気診断など) を除く、介入および非介入手順から生じる観察結果が含まれる。 通常、検査結果は臨床医によって生成され、検査中に行われたコンポーネントの観察に関するより詳細な情報を提供する。 例としては、消化器内科医が大腸内視鏡検査中に観察されたポリープのサイズを報告する場合がある。</t>
+    <t>他の手順によって生成された観察結果。このカテゴリーには介入および、検査および画像診断を除く非介入の手順から得られた観察結果が含まれる（例：心臓カテーテル検査、内視鏡検査、電気診断など）。 この観察結果は通常、手順中に得られた個々の観察結果について、より詳細な情報を提供するために臨床医によって生成される。 例としては、大腸内視鏡検査中に観察されたポリープの大きさを消化器専門医が報告する場合などが挙げられる。</t>
   </si>
   <si>
     <t>survey</t>

--- a/jpcore-r4/develop/CodeSystem-jp-simpleobservationcategory-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-simpleobservationcategory-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>
